--- a/dataAcquisition/parseEventData/aliasReports/DAR_alias_check.xlsx
+++ b/dataAcquisition/parseEventData/aliasReports/DAR_alias_check.xlsx
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="5494" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="7094" uniqueCount="157">
   <si>
     <t>Raw_Name_From_File</t>
   </si>
@@ -495,6 +495,24 @@
   </si>
   <si>
     <t>R19</t>
+  </si>
+  <si>
+    <t>Mechanics R'Us</t>
+  </si>
+  <si>
+    <t>Christchurch Super 440</t>
+  </si>
+  <si>
+    <t>Darwin Triple Crowm</t>
+  </si>
+  <si>
+    <t>Darwin Triple Crown</t>
+  </si>
+  <si>
+    <t>Darwin Tripple Crown</t>
+  </si>
+  <si>
+    <t>betr Darwin Triple Crown</t>
   </si>
 </sst>
 </file>
@@ -964,10 +982,10 @@
   <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19" customWidth="true"/>
-    <col min="2" max="2" width="16.81640625" customWidth="true"/>
-    <col min="3" max="3" width="10" customWidth="true"/>
-    <col min="4" max="4" width="12.81640625" customWidth="true"/>
+    <col min="1" max="1" width="19.109375" customWidth="true"/>
+    <col min="2" max="2" width="16.6640625" customWidth="true"/>
+    <col min="3" max="3" width="9.77734375" customWidth="true"/>
+    <col min="4" max="4" width="12.88671875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -986,10 +1004,10 @@
     </row>
     <row r="2">
       <c r="A2" s="38" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C2" s="38" t="s">
         <v>33</v>
@@ -1000,10 +1018,10 @@
     </row>
     <row r="3">
       <c r="A3" s="38" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B3" s="38" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C3" s="38" t="s">
         <v>33</v>
@@ -1014,10 +1032,10 @@
     </row>
     <row r="4">
       <c r="A4" s="38" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="B4" s="38" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="C4" s="38" t="s">
         <v>33</v>
@@ -1028,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" s="38" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="B5" s="38" t="s">
-        <v>4</v>
+        <v>151</v>
       </c>
       <c r="C5" s="38" t="s">
         <v>33</v>
@@ -1042,10 +1060,10 @@
     </row>
     <row r="6">
       <c r="A6" s="38" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" s="38" t="s">
         <v>33</v>
@@ -1056,10 +1074,10 @@
     </row>
     <row r="7">
       <c r="A7" s="38" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="38" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="C7" s="38" t="s">
         <v>33</v>
@@ -1070,10 +1088,10 @@
     </row>
     <row r="8">
       <c r="A8" s="38" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C8" s="38" t="s">
         <v>33</v>
@@ -1084,10 +1102,10 @@
     </row>
     <row r="9">
       <c r="A9" s="38" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="38" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C9" s="38" t="s">
         <v>33</v>
@@ -1098,10 +1116,10 @@
     </row>
     <row r="10">
       <c r="A10" s="38" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="38" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" s="38" t="s">
         <v>33</v>
@@ -1112,10 +1130,10 @@
     </row>
     <row r="11">
       <c r="A11" s="38" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="38" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" s="38" t="s">
         <v>33</v>
@@ -1126,10 +1144,10 @@
     </row>
     <row r="12">
       <c r="A12" s="38" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" s="38" t="s">
         <v>33</v>
@@ -1140,10 +1158,10 @@
     </row>
     <row r="13">
       <c r="A13" s="38" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" s="38" t="s">
         <v>33</v>
@@ -1154,10 +1172,10 @@
     </row>
     <row r="14">
       <c r="A14" s="38" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>13</v>
+        <v>151</v>
       </c>
       <c r="C14" s="38" t="s">
         <v>33</v>
@@ -1168,10 +1186,10 @@
     </row>
     <row r="15">
       <c r="A15" s="38" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C15" s="38" t="s">
         <v>33</v>
@@ -1182,10 +1200,10 @@
     </row>
     <row r="16">
       <c r="A16" s="38" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C16" s="38" t="s">
         <v>33</v>
@@ -1196,10 +1214,10 @@
     </row>
     <row r="17">
       <c r="A17" s="38" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C17" s="38" t="s">
         <v>33</v>
@@ -1210,10 +1228,10 @@
     </row>
     <row r="18">
       <c r="A18" s="38" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C18" s="38" t="s">
         <v>33</v>
@@ -1224,10 +1242,10 @@
     </row>
     <row r="19">
       <c r="A19" s="38" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C19" s="38" t="s">
         <v>33</v>
@@ -1238,10 +1256,10 @@
     </row>
     <row r="20">
       <c r="A20" s="38" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C20" s="38" t="s">
         <v>33</v>
@@ -1252,10 +1270,10 @@
     </row>
     <row r="21">
       <c r="A21" s="38" t="s">
-        <v>132</v>
+        <v>18</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>132</v>
+        <v>18</v>
       </c>
       <c r="C21" s="38" t="s">
         <v>33</v>
@@ -1266,10 +1284,10 @@
     </row>
     <row r="22">
       <c r="A22" s="38" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C22" s="38" t="s">
         <v>33</v>
@@ -1280,10 +1298,10 @@
     </row>
     <row r="23">
       <c r="A23" s="38" t="s">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="C23" s="38" t="s">
         <v>33</v>
@@ -1294,10 +1312,10 @@
     </row>
     <row r="24">
       <c r="A24" s="38" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C24" s="38" t="s">
         <v>33</v>
@@ -1308,10 +1326,10 @@
     </row>
     <row r="25">
       <c r="A25" s="38" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C25" s="38" t="s">
         <v>33</v>
@@ -1322,10 +1340,10 @@
     </row>
     <row r="26">
       <c r="A26" s="38" t="s">
-        <v>133</v>
+        <v>22</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>133</v>
+        <v>22</v>
       </c>
       <c r="C26" s="38" t="s">
         <v>33</v>
@@ -1336,10 +1354,10 @@
     </row>
     <row r="27">
       <c r="A27" s="38" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C27" s="38" t="s">
         <v>33</v>
@@ -1350,10 +1368,10 @@
     </row>
     <row r="28">
       <c r="A28" s="38" t="s">
-        <v>25</v>
+        <v>133</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>25</v>
+        <v>133</v>
       </c>
       <c r="C28" s="38" t="s">
         <v>33</v>
@@ -1364,18 +1382,30 @@
     </row>
     <row r="29">
       <c r="A29" s="38" t="s">
-        <v>112</v>
+        <v>24</v>
+      </c>
+      <c r="B29" s="0" t="s">
+        <v>31</v>
       </c>
       <c r="C29" s="38" t="s">
-        <v>34</v>
+        <v>33</v>
+      </c>
+      <c r="D29" s="0" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="38" t="s">
-        <v>26</v>
+        <v>25</v>
+      </c>
+      <c r="B30" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="C30" s="38" t="s">
-        <v>34</v>
+        <v>33</v>
+      </c>
+      <c r="D30" s="0" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1384,13 +1414,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19" customWidth="true"/>
-    <col min="2" max="2" width="16.81640625" customWidth="true"/>
-    <col min="3" max="3" width="6" customWidth="true"/>
-    <col min="4" max="4" width="12.81640625" customWidth="true"/>
+    <col min="1" max="1" width="20.109375" customWidth="true"/>
+    <col min="2" max="2" width="16.6640625" customWidth="true"/>
+    <col min="3" max="3" width="9.77734375" customWidth="true"/>
+    <col min="4" max="4" width="12.88671875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1409,7 +1439,7 @@
     </row>
     <row r="2">
       <c r="A2" s="40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B2" s="40" t="s">
         <v>105</v>
@@ -1423,7 +1453,7 @@
     </row>
     <row r="3">
       <c r="A3" s="40" t="s">
-        <v>41</v>
+        <v>153</v>
       </c>
       <c r="B3" s="40" t="s">
         <v>105</v>
@@ -1437,10 +1467,10 @@
     </row>
     <row r="4">
       <c r="A4" s="40" t="s">
-        <v>37</v>
+        <v>154</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>42</v>
+        <v>105</v>
       </c>
       <c r="C4" s="40" t="s">
         <v>33</v>
@@ -1451,23 +1481,55 @@
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="0"/>
+        <v>155</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>105</v>
+      </c>
       <c r="C5" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="0"/>
+        <v>33</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="0"/>
+      <c r="B6" s="0" t="s">
+        <v>105</v>
+      </c>
       <c r="C6" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="s">
+        <v>156</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="s">
+        <v>152</v>
+      </c>
+      <c r="B8" s="0"/>
+      <c r="C8" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="0"/>
+      <c r="D8" s="0"/>
     </row>
   </sheetData>
 </worksheet>
@@ -1478,10 +1540,10 @@
   <dimension ref="A1:D59"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19" customWidth="true"/>
-    <col min="2" max="2" width="16.81640625" customWidth="true"/>
-    <col min="3" max="3" width="10" customWidth="true"/>
-    <col min="4" max="4" width="12.81640625" customWidth="true"/>
+    <col min="1" max="1" width="26.88671875" customWidth="true"/>
+    <col min="2" max="2" width="16.6640625" customWidth="true"/>
+    <col min="3" max="3" width="9.77734375" customWidth="true"/>
+    <col min="4" max="4" width="12.88671875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1500,10 +1562,10 @@
     </row>
     <row r="2">
       <c r="A2" s="42" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="B2" s="42" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C2" s="42" t="s">
         <v>33</v>
@@ -1514,10 +1576,10 @@
     </row>
     <row r="3">
       <c r="A3" s="42" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="B3" s="42" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="C3" s="42" t="s">
         <v>33</v>
@@ -1528,10 +1590,10 @@
     </row>
     <row r="4">
       <c r="A4" s="42" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="B4" s="42" t="s">
-        <v>129</v>
+        <v>81</v>
       </c>
       <c r="C4" s="42" t="s">
         <v>33</v>
@@ -1542,10 +1604,10 @@
     </row>
     <row r="5">
       <c r="A5" s="42" t="s">
-        <v>134</v>
+        <v>73</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>149</v>
+        <v>81</v>
       </c>
       <c r="C5" s="42" t="s">
         <v>33</v>
@@ -1556,10 +1618,10 @@
     </row>
     <row r="6">
       <c r="A6" s="42" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="C6" s="42" t="s">
         <v>33</v>
@@ -1570,10 +1632,10 @@
     </row>
     <row r="7">
       <c r="A7" s="42" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="B7" s="42" t="s">
-        <v>131</v>
+        <v>81</v>
       </c>
       <c r="C7" s="42" t="s">
         <v>33</v>
@@ -1584,10 +1646,10 @@
     </row>
     <row r="8">
       <c r="A8" s="42" t="s">
-        <v>136</v>
+        <v>47</v>
       </c>
       <c r="B8" s="42" t="s">
-        <v>150</v>
+        <v>82</v>
       </c>
       <c r="C8" s="42" t="s">
         <v>33</v>
@@ -1598,10 +1660,10 @@
     </row>
     <row r="9">
       <c r="A9" s="42" t="s">
-        <v>128</v>
+        <v>48</v>
       </c>
       <c r="B9" s="42" t="s">
-        <v>129</v>
+        <v>82</v>
       </c>
       <c r="C9" s="42" t="s">
         <v>33</v>
@@ -1612,10 +1674,10 @@
     </row>
     <row r="10">
       <c r="A10" s="42" t="s">
-        <v>148</v>
+        <v>49</v>
       </c>
       <c r="B10" s="42" t="s">
-        <v>149</v>
+        <v>83</v>
       </c>
       <c r="C10" s="42" t="s">
         <v>33</v>
@@ -1626,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" s="42" t="s">
-        <v>67</v>
+        <v>115</v>
       </c>
       <c r="B11" s="42" t="s">
-        <v>81</v>
+        <v>129</v>
       </c>
       <c r="C11" s="42" t="s">
         <v>33</v>
@@ -1640,10 +1702,10 @@
     </row>
     <row r="12">
       <c r="A12" s="42" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="B12" s="42" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="C12" s="42" t="s">
         <v>33</v>
@@ -1654,10 +1716,10 @@
     </row>
     <row r="13">
       <c r="A13" s="42" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="B13" s="42" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="C13" s="42" t="s">
         <v>33</v>
@@ -1668,10 +1730,10 @@
     </row>
     <row r="14">
       <c r="A14" s="42" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B14" s="42" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="C14" s="42" t="s">
         <v>33</v>
@@ -1682,10 +1744,10 @@
     </row>
     <row r="15">
       <c r="A15" s="42" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="B15" s="42" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="C15" s="42" t="s">
         <v>33</v>
@@ -1696,10 +1758,10 @@
     </row>
     <row r="16">
       <c r="A16" s="42" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="B16" s="42" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="C16" s="42" t="s">
         <v>33</v>
@@ -1710,10 +1772,10 @@
     </row>
     <row r="17">
       <c r="A17" s="42" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="B17" s="42" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="C17" s="42" t="s">
         <v>33</v>
@@ -1724,10 +1786,10 @@
     </row>
     <row r="18">
       <c r="A18" s="42" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="B18" s="42" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="C18" s="42" t="s">
         <v>33</v>
@@ -1738,10 +1800,10 @@
     </row>
     <row r="19">
       <c r="A19" s="42" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="B19" s="42" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="C19" s="42" t="s">
         <v>33</v>
@@ -1752,10 +1814,10 @@
     </row>
     <row r="20">
       <c r="A20" s="42" t="s">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="B20" s="42" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="C20" s="42" t="s">
         <v>33</v>
@@ -1766,10 +1828,10 @@
     </row>
     <row r="21">
       <c r="A21" s="42" t="s">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="B21" s="42" t="s">
-        <v>104</v>
+        <v>149</v>
       </c>
       <c r="C21" s="42" t="s">
         <v>33</v>
@@ -1780,10 +1842,10 @@
     </row>
     <row r="22">
       <c r="A22" s="42" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="B22" s="42" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="C22" s="42" t="s">
         <v>33</v>
@@ -1794,7 +1856,7 @@
     </row>
     <row r="23">
       <c r="A23" s="42" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B23" s="42" t="s">
         <v>149</v>
@@ -1808,10 +1870,10 @@
     </row>
     <row r="24">
       <c r="A24" s="42" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B24" s="42" t="s">
-        <v>80</v>
+        <v>149</v>
       </c>
       <c r="C24" s="42" t="s">
         <v>33</v>
@@ -1822,10 +1884,10 @@
     </row>
     <row r="25">
       <c r="A25" s="42" t="s">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="B25" s="42" t="s">
-        <v>104</v>
+        <v>149</v>
       </c>
       <c r="C25" s="42" t="s">
         <v>33</v>
@@ -1836,10 +1898,10 @@
     </row>
     <row r="26">
       <c r="A26" s="42" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="B26" s="42" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="C26" s="42" t="s">
         <v>33</v>
@@ -1850,10 +1912,10 @@
     </row>
     <row r="27">
       <c r="A27" s="42" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="B27" s="42" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="C27" s="42" t="s">
         <v>33</v>
@@ -1864,10 +1926,10 @@
     </row>
     <row r="28">
       <c r="A28" s="42" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="B28" s="42" t="s">
-        <v>104</v>
+        <v>149</v>
       </c>
       <c r="C28" s="42" t="s">
         <v>33</v>
@@ -1878,10 +1940,10 @@
     </row>
     <row r="29">
       <c r="A29" s="42" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="B29" s="42" t="s">
-        <v>129</v>
+        <v>81</v>
       </c>
       <c r="C29" s="42" t="s">
         <v>33</v>
@@ -1892,10 +1954,10 @@
     </row>
     <row r="30">
       <c r="A30" s="42" t="s">
-        <v>143</v>
+        <v>101</v>
       </c>
       <c r="B30" s="42" t="s">
-        <v>149</v>
+        <v>104</v>
       </c>
       <c r="C30" s="42" t="s">
         <v>33</v>
@@ -1906,7 +1968,7 @@
     </row>
     <row r="31">
       <c r="A31" s="42" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B31" s="42" t="s">
         <v>129</v>
@@ -1920,7 +1982,7 @@
     </row>
     <row r="32">
       <c r="A32" s="42" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B32" s="42" t="s">
         <v>149</v>
@@ -1934,7 +1996,7 @@
     </row>
     <row r="33">
       <c r="A33" s="42" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="B33" s="42" t="s">
         <v>104</v>
@@ -1948,7 +2010,7 @@
     </row>
     <row r="34">
       <c r="A34" s="42" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B34" s="42" t="s">
         <v>129</v>
@@ -1962,7 +2024,7 @@
     </row>
     <row r="35">
       <c r="A35" s="42" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B35" s="42" t="s">
         <v>149</v>
@@ -1976,7 +2038,7 @@
     </row>
     <row r="36">
       <c r="A36" s="42" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B36" s="42" t="s">
         <v>129</v>
@@ -1990,7 +2052,7 @@
     </row>
     <row r="37">
       <c r="A37" s="42" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B37" s="42" t="s">
         <v>149</v>
@@ -2004,10 +2066,10 @@
     </row>
     <row r="38">
       <c r="A38" s="42" t="s">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="B38" s="42" t="s">
-        <v>131</v>
+        <v>104</v>
       </c>
       <c r="C38" s="42" t="s">
         <v>33</v>
@@ -2018,10 +2080,10 @@
     </row>
     <row r="39">
       <c r="A39" s="42" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="B39" s="42" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="C39" s="42" t="s">
         <v>33</v>
@@ -2032,10 +2094,10 @@
     </row>
     <row r="40">
       <c r="A40" s="42" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="B40" s="42" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="C40" s="42" t="s">
         <v>33</v>
@@ -2046,7 +2108,7 @@
     </row>
     <row r="41">
       <c r="A41" s="42" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B41" s="42" t="s">
         <v>129</v>
@@ -2060,10 +2122,10 @@
     </row>
     <row r="42">
       <c r="A42" s="42" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="B42" s="42" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C42" s="42" t="s">
         <v>33</v>
@@ -2074,10 +2136,10 @@
     </row>
     <row r="43">
       <c r="A43" s="42" t="s">
-        <v>65</v>
+        <v>131</v>
       </c>
       <c r="B43" s="42" t="s">
-        <v>81</v>
+        <v>131</v>
       </c>
       <c r="C43" s="42" t="s">
         <v>33</v>
@@ -2088,10 +2150,10 @@
     </row>
     <row r="44">
       <c r="A44" s="42" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="B44" s="42" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="C44" s="42" t="s">
         <v>33</v>
@@ -2102,10 +2164,10 @@
     </row>
     <row r="45">
       <c r="A45" s="42" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="B45" s="42" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="C45" s="42" t="s">
         <v>33</v>
@@ -2116,10 +2178,10 @@
     </row>
     <row r="46">
       <c r="A46" s="42" t="s">
-        <v>66</v>
+        <v>126</v>
       </c>
       <c r="B46" s="42" t="s">
-        <v>81</v>
+        <v>149</v>
       </c>
       <c r="C46" s="42" t="s">
         <v>33</v>
@@ -2130,10 +2192,10 @@
     </row>
     <row r="47">
       <c r="A47" s="42" t="s">
-        <v>67</v>
+        <v>136</v>
       </c>
       <c r="B47" s="42" t="s">
-        <v>81</v>
+        <v>150</v>
       </c>
       <c r="C47" s="42" t="s">
         <v>33</v>
@@ -2144,7 +2206,7 @@
     </row>
     <row r="48">
       <c r="A48" s="42" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B48" s="42" t="s">
         <v>81</v>
@@ -2158,58 +2220,100 @@
     </row>
     <row r="49">
       <c r="A49" s="42" t="s">
-        <v>69</v>
+        <v>127</v>
+      </c>
+      <c r="B49" s="0" t="s">
+        <v>81</v>
       </c>
       <c r="C49" s="42" t="s">
-        <v>97</v>
+        <v>33</v>
+      </c>
+      <c r="D49" s="0" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="42" t="s">
-        <v>71</v>
+        <v>147</v>
+      </c>
+      <c r="B50" s="0" t="s">
+        <v>81</v>
       </c>
       <c r="C50" s="42" t="s">
-        <v>97</v>
+        <v>33</v>
+      </c>
+      <c r="D50" s="0" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="42" t="s">
-        <v>107</v>
+        <v>128</v>
+      </c>
+      <c r="B51" s="0" t="s">
+        <v>129</v>
       </c>
       <c r="C51" s="42" t="s">
-        <v>97</v>
+        <v>33</v>
+      </c>
+      <c r="D51" s="0" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="42" t="s">
-        <v>73</v>
+        <v>148</v>
+      </c>
+      <c r="B52" s="0" t="s">
+        <v>149</v>
       </c>
       <c r="C52" s="42" t="s">
-        <v>97</v>
+        <v>33</v>
+      </c>
+      <c r="D52" s="0" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="42" t="s">
-        <v>74</v>
+        <v>103</v>
+      </c>
+      <c r="B53" s="0" t="s">
+        <v>81</v>
       </c>
       <c r="C53" s="42" t="s">
-        <v>97</v>
+        <v>33</v>
+      </c>
+      <c r="D53" s="0" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="42" t="s">
-        <v>114</v>
+        <v>67</v>
+      </c>
+      <c r="B54" s="0" t="s">
+        <v>81</v>
       </c>
       <c r="C54" s="42" t="s">
-        <v>97</v>
+        <v>33</v>
+      </c>
+      <c r="D54" s="0" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="42" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="B55" s="0" t="s">
+        <v>81</v>
       </c>
       <c r="C55" s="42" t="s">
-        <v>97</v>
+        <v>33</v>
+      </c>
+      <c r="D55" s="0" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="56">
